--- a/娱乐/LanotaPlugin/Data/excel_table/Lanota定数表_2026春.xlsx
+++ b/娱乐/LanotaPlugin/Data/excel_table/Lanota定数表_2026春.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wangp\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6cb025f0052b68ec/0跑团相关/OlivOS青果相关/青果插件/Desom-OlivaDice-Plugin/娱乐/BiliShareInfo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB42E0B5-19D9-4C48-94F6-DA404D0693AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{FB42E0B5-19D9-4C48-94F6-DA404D0693AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF592268-3198-4D40-AF04-9B7595C4405C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1178,7 +1181,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="新細明體"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -1189,7 +1192,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="新細明體"/>
+        <rFont val="等线"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -1209,7 +1212,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="新細明體"/>
+        <rFont val="等线"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -1254,10 +1257,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Z-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Event-97</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1432,6 +1431,10 @@
   </si>
   <si>
     <t>Re：End of a Dream</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1442,24 +1445,24 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1467,7 +1470,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1475,7 +1478,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="新細明體"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1527,7 +1530,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1806,7 +1809,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F190"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" style="2"/>
     <col min="2" max="2" width="50.625" style="1" customWidth="1"/>
@@ -1816,7 +1819,7 @@
     <col min="6" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1832,7 +1835,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1">
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1848,7 +1851,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" ht="18" customHeight="1">
+    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1864,7 +1867,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" ht="18" customHeight="1">
+    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1880,7 +1883,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1">
+    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -1900,7 +1903,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1">
+    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1916,7 +1919,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1">
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -1932,7 +1935,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1">
+    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -1948,7 +1951,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1">
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1968,12 +1971,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1">
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
@@ -1984,7 +1987,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1">
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -2000,7 +2003,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1">
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
@@ -2020,7 +2023,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1">
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
@@ -2036,7 +2039,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1">
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
@@ -2056,7 +2059,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1">
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
@@ -2067,12 +2070,12 @@
         <v>1</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:6" ht="18" customHeight="1">
+    <row r="16" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
@@ -2088,7 +2091,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1">
+    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -2104,7 +2107,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6" ht="18" customHeight="1">
+    <row r="18" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -2124,7 +2127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18" customHeight="1">
+    <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -2144,7 +2147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1">
+    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>42</v>
       </c>
@@ -2160,7 +2163,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1">
+    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>43</v>
       </c>
@@ -2176,7 +2179,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1">
+    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>44</v>
       </c>
@@ -2192,7 +2195,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1">
+    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -2208,7 +2211,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1">
+    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -2224,12 +2227,12 @@
       <c r="E24" s="1"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1">
+    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>1</v>
@@ -2240,7 +2243,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1">
+    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>49</v>
       </c>
@@ -2256,7 +2259,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1">
+    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>51</v>
       </c>
@@ -2272,7 +2275,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1">
+    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>52</v>
       </c>
@@ -2288,7 +2291,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1">
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>53</v>
       </c>
@@ -2304,7 +2307,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1">
+    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>54</v>
       </c>
@@ -2320,12 +2323,12 @@
       <c r="E30" s="1"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" ht="18" customHeight="1">
+    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>1</v>
@@ -2336,7 +2339,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1">
+    <row r="32" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>56</v>
       </c>
@@ -2352,7 +2355,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="2"/>
     </row>
-    <row r="33" spans="1:6" ht="18" customHeight="1">
+    <row r="33" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>57</v>
       </c>
@@ -2368,7 +2371,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="2"/>
     </row>
-    <row r="34" spans="1:6" ht="18" customHeight="1">
+    <row r="34" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
@@ -2384,7 +2387,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" ht="18" customHeight="1">
+    <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>60</v>
       </c>
@@ -2400,7 +2403,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="2"/>
     </row>
-    <row r="36" spans="1:6" ht="18" customHeight="1">
+    <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>62</v>
       </c>
@@ -2416,7 +2419,7 @@
       <c r="E36" s="1"/>
       <c r="F36" s="2"/>
     </row>
-    <row r="37" spans="1:6" ht="18" customHeight="1">
+    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>64</v>
       </c>
@@ -2432,7 +2435,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="2"/>
     </row>
-    <row r="38" spans="1:6" ht="18" customHeight="1">
+    <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>65</v>
       </c>
@@ -2448,12 +2451,12 @@
       <c r="E38" s="1"/>
       <c r="F38" s="2"/>
     </row>
-    <row r="39" spans="1:6" ht="18" customHeight="1">
+    <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>1</v>
@@ -2464,7 +2467,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="2"/>
     </row>
-    <row r="40" spans="1:6" ht="18" customHeight="1">
+    <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>66</v>
       </c>
@@ -2480,7 +2483,7 @@
       <c r="E40" s="1"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="1:6" ht="18" customHeight="1">
+    <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>67</v>
       </c>
@@ -2496,7 +2499,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="1:6" ht="18" customHeight="1">
+    <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>68</v>
       </c>
@@ -2512,7 +2515,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="1:6" ht="18" customHeight="1">
+    <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>70</v>
       </c>
@@ -2528,7 +2531,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="1:6" ht="18" customHeight="1">
+    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>71</v>
       </c>
@@ -2544,7 +2547,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="1:6" ht="18" customHeight="1">
+    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>72</v>
       </c>
@@ -2560,7 +2563,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="2"/>
     </row>
-    <row r="46" spans="1:6" ht="18" customHeight="1">
+    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>73</v>
       </c>
@@ -2576,7 +2579,7 @@
       <c r="E46" s="1"/>
       <c r="F46" s="2"/>
     </row>
-    <row r="47" spans="1:6" ht="18" customHeight="1">
+    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>74</v>
       </c>
@@ -2592,7 +2595,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="2"/>
     </row>
-    <row r="48" spans="1:6" ht="18" customHeight="1">
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>75</v>
       </c>
@@ -2608,7 +2611,7 @@
       <c r="E48" s="1"/>
       <c r="F48" s="2"/>
     </row>
-    <row r="49" spans="1:6" ht="18" customHeight="1">
+    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>77</v>
       </c>
@@ -2624,7 +2627,7 @@
       <c r="E49" s="1"/>
       <c r="F49" s="2"/>
     </row>
-    <row r="50" spans="1:6" ht="18" customHeight="1">
+    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>79</v>
       </c>
@@ -2640,7 +2643,7 @@
       <c r="E50" s="1"/>
       <c r="F50" s="2"/>
     </row>
-    <row r="51" spans="1:6" ht="18" customHeight="1">
+    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>80</v>
       </c>
@@ -2656,7 +2659,7 @@
       <c r="E51" s="1"/>
       <c r="F51" s="2"/>
     </row>
-    <row r="52" spans="1:6" ht="18" customHeight="1">
+    <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>307</v>
       </c>
@@ -2672,7 +2675,7 @@
       <c r="E52" s="1"/>
       <c r="F52" s="2"/>
     </row>
-    <row r="53" spans="1:6" ht="18" customHeight="1">
+    <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>308</v>
       </c>
@@ -2688,7 +2691,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="2"/>
     </row>
-    <row r="54" spans="1:6" ht="18" customHeight="1">
+    <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>202</v>
       </c>
@@ -2703,7 +2706,7 @@
       </c>
       <c r="F54" s="2"/>
     </row>
-    <row r="55" spans="1:6" ht="18" customHeight="1">
+    <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>204</v>
       </c>
@@ -2718,7 +2721,7 @@
       </c>
       <c r="F55" s="2"/>
     </row>
-    <row r="56" spans="1:6" ht="18" customHeight="1">
+    <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>206</v>
       </c>
@@ -2733,7 +2736,7 @@
       </c>
       <c r="F56" s="2"/>
     </row>
-    <row r="57" spans="1:6" ht="18" customHeight="1">
+    <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>208</v>
       </c>
@@ -2748,7 +2751,7 @@
       </c>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" spans="1:6" ht="18" customHeight="1">
+    <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>210</v>
       </c>
@@ -2763,7 +2766,7 @@
       </c>
       <c r="F58" s="2"/>
     </row>
-    <row r="59" spans="1:6" ht="18" customHeight="1">
+    <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>341</v>
       </c>
@@ -2777,9 +2780,9 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="18" customHeight="1">
+    <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>342</v>
+        <v>389</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>326</v>
@@ -2791,7 +2794,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="18" customHeight="1">
+    <row r="61" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>81</v>
       </c>
@@ -2807,7 +2810,7 @@
       <c r="E61" s="1"/>
       <c r="F61" s="2"/>
     </row>
-    <row r="62" spans="1:6" ht="18" customHeight="1">
+    <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>83</v>
       </c>
@@ -2823,7 +2826,7 @@
       <c r="E62" s="1"/>
       <c r="F62" s="2"/>
     </row>
-    <row r="63" spans="1:6" ht="18" customHeight="1">
+    <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>85</v>
       </c>
@@ -2839,7 +2842,7 @@
       <c r="E63" s="1"/>
       <c r="F63" s="2"/>
     </row>
-    <row r="64" spans="1:6" ht="18" customHeight="1">
+    <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>87</v>
       </c>
@@ -2855,7 +2858,7 @@
       <c r="E64" s="1"/>
       <c r="F64" s="2"/>
     </row>
-    <row r="65" spans="1:6" ht="18" customHeight="1">
+    <row r="65" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>89</v>
       </c>
@@ -2871,12 +2874,12 @@
       <c r="E65" s="1"/>
       <c r="F65" s="2"/>
     </row>
-    <row r="66" spans="1:6" ht="18" customHeight="1">
+    <row r="66" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>1</v>
@@ -2887,7 +2890,7 @@
       <c r="E66" s="1"/>
       <c r="F66" s="2"/>
     </row>
-    <row r="67" spans="1:6" ht="18" customHeight="1">
+    <row r="67" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>92</v>
       </c>
@@ -2903,12 +2906,12 @@
       <c r="E67" s="1"/>
       <c r="F67" s="2"/>
     </row>
-    <row r="68" spans="1:6" ht="18" customHeight="1">
+    <row r="68" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>1</v>
@@ -2919,7 +2922,7 @@
       <c r="E68" s="1"/>
       <c r="F68" s="2"/>
     </row>
-    <row r="69" spans="1:6" ht="18" customHeight="1">
+    <row r="69" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>95</v>
       </c>
@@ -2935,7 +2938,7 @@
       <c r="E69" s="1"/>
       <c r="F69" s="2"/>
     </row>
-    <row r="70" spans="1:6" ht="18" customHeight="1">
+    <row r="70" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>97</v>
       </c>
@@ -2951,7 +2954,7 @@
       <c r="E70" s="1"/>
       <c r="F70" s="2"/>
     </row>
-    <row r="71" spans="1:6" ht="18" customHeight="1">
+    <row r="71" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>98</v>
       </c>
@@ -2967,7 +2970,7 @@
       <c r="E71" s="1"/>
       <c r="F71" s="2"/>
     </row>
-    <row r="72" spans="1:6" ht="18" customHeight="1">
+    <row r="72" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>100</v>
       </c>
@@ -2983,7 +2986,7 @@
       <c r="E72" s="1"/>
       <c r="F72" s="2"/>
     </row>
-    <row r="73" spans="1:6" ht="18" customHeight="1">
+    <row r="73" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>101</v>
       </c>
@@ -2999,12 +3002,12 @@
       <c r="E73" s="1"/>
       <c r="F73" s="2"/>
     </row>
-    <row r="74" spans="1:6" ht="18" customHeight="1">
+    <row r="74" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>1</v>
@@ -3015,7 +3018,7 @@
       <c r="E74" s="1"/>
       <c r="F74" s="2"/>
     </row>
-    <row r="75" spans="1:6" ht="18" customHeight="1">
+    <row r="75" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>102</v>
       </c>
@@ -3031,7 +3034,7 @@
       <c r="E75" s="1"/>
       <c r="F75" s="2"/>
     </row>
-    <row r="76" spans="1:6" ht="18" customHeight="1">
+    <row r="76" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>103</v>
       </c>
@@ -3047,7 +3050,7 @@
       <c r="E76" s="1"/>
       <c r="F76" s="2"/>
     </row>
-    <row r="77" spans="1:6" ht="18" customHeight="1">
+    <row r="77" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>105</v>
       </c>
@@ -3063,7 +3066,7 @@
       <c r="E77" s="1"/>
       <c r="F77" s="2"/>
     </row>
-    <row r="78" spans="1:6" ht="18" customHeight="1">
+    <row r="78" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>106</v>
       </c>
@@ -3077,7 +3080,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="18" customHeight="1">
+    <row r="79" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>108</v>
       </c>
@@ -3093,7 +3096,7 @@
       <c r="E79" s="1"/>
       <c r="F79" s="2"/>
     </row>
-    <row r="80" spans="1:6" ht="18" customHeight="1">
+    <row r="80" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>110</v>
       </c>
@@ -3113,7 +3116,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="18" customHeight="1">
+    <row r="81" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>293</v>
       </c>
@@ -3129,7 +3132,7 @@
       <c r="E81" s="1"/>
       <c r="F81" s="2"/>
     </row>
-    <row r="82" spans="1:6" ht="18" customHeight="1">
+    <row r="82" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>292</v>
       </c>
@@ -3145,12 +3148,12 @@
       <c r="E82" s="1"/>
       <c r="F82" s="2"/>
     </row>
-    <row r="83" spans="1:6" ht="18" customHeight="1">
+    <row r="83" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>212</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>1</v>
@@ -3160,7 +3163,7 @@
       </c>
       <c r="F83" s="2"/>
     </row>
-    <row r="84" spans="1:6" ht="18" customHeight="1">
+    <row r="84" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>213</v>
       </c>
@@ -3175,7 +3178,7 @@
       </c>
       <c r="F84" s="2"/>
     </row>
-    <row r="85" spans="1:6" ht="18" customHeight="1">
+    <row r="85" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>215</v>
       </c>
@@ -3190,7 +3193,7 @@
       </c>
       <c r="F85" s="2"/>
     </row>
-    <row r="86" spans="1:6" ht="18" customHeight="1">
+    <row r="86" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>217</v>
       </c>
@@ -3205,7 +3208,7 @@
       </c>
       <c r="F86" s="2"/>
     </row>
-    <row r="87" spans="1:6" ht="18" customHeight="1">
+    <row r="87" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>219</v>
       </c>
@@ -3220,7 +3223,7 @@
       </c>
       <c r="F87" s="2"/>
     </row>
-    <row r="88" spans="1:6" ht="18" customHeight="1">
+    <row r="88" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>221</v>
       </c>
@@ -3235,7 +3238,7 @@
       </c>
       <c r="F88" s="2"/>
     </row>
-    <row r="89" spans="1:6" ht="18" customHeight="1">
+    <row r="89" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>223</v>
       </c>
@@ -3250,7 +3253,7 @@
       </c>
       <c r="F89" s="2"/>
     </row>
-    <row r="90" spans="1:6" ht="18" customHeight="1">
+    <row r="90" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>225</v>
       </c>
@@ -3265,7 +3268,7 @@
       </c>
       <c r="F90" s="2"/>
     </row>
-    <row r="91" spans="1:6" ht="18" customHeight="1">
+    <row r="91" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>227</v>
       </c>
@@ -3280,7 +3283,7 @@
       </c>
       <c r="F91" s="2"/>
     </row>
-    <row r="92" spans="1:6" ht="18" customHeight="1">
+    <row r="92" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>229</v>
       </c>
@@ -3295,12 +3298,12 @@
       </c>
       <c r="F92" s="2"/>
     </row>
-    <row r="93" spans="1:6" ht="18" customHeight="1">
+    <row r="93" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>231</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>1</v>
@@ -3310,7 +3313,7 @@
       </c>
       <c r="E93" s="1"/>
     </row>
-    <row r="94" spans="1:6" ht="18" customHeight="1">
+    <row r="94" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>232</v>
       </c>
@@ -3324,7 +3327,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="18" customHeight="1">
+    <row r="95" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>290</v>
       </c>
@@ -3338,7 +3341,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="18" customHeight="1">
+    <row r="96" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>288</v>
       </c>
@@ -3352,7 +3355,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="18" customHeight="1">
+    <row r="97" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>333</v>
       </c>
@@ -3366,7 +3369,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="18" customHeight="1">
+    <row r="98" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>334</v>
       </c>
@@ -3380,9 +3383,9 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="18" customHeight="1">
+    <row r="99" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>317</v>
@@ -3400,7 +3403,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="18" customHeight="1">
+    <row r="100" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>335</v>
       </c>
@@ -3414,7 +3417,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="18" customHeight="1">
+    <row r="101" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>336</v>
       </c>
@@ -3428,7 +3431,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="18" customHeight="1">
+    <row r="102" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>338</v>
       </c>
@@ -3442,7 +3445,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="18" customHeight="1">
+    <row r="103" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>340</v>
       </c>
@@ -3456,9 +3459,9 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="18" customHeight="1">
+    <row r="104" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>329</v>
@@ -3470,9 +3473,9 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="18" customHeight="1">
+    <row r="105" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>330</v>
@@ -3484,9 +3487,9 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="18" customHeight="1">
+    <row r="106" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>331</v>
@@ -3498,7 +3501,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="18" customHeight="1">
+    <row r="107" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>111</v>
       </c>
@@ -3514,7 +3517,7 @@
       <c r="E107" s="1"/>
       <c r="F107" s="2"/>
     </row>
-    <row r="108" spans="1:6" ht="18" customHeight="1">
+    <row r="108" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>112</v>
       </c>
@@ -3530,7 +3533,7 @@
       <c r="E108" s="1"/>
       <c r="F108" s="2"/>
     </row>
-    <row r="109" spans="1:6" ht="18" customHeight="1">
+    <row r="109" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>113</v>
       </c>
@@ -3546,7 +3549,7 @@
       <c r="E109" s="1"/>
       <c r="F109" s="2"/>
     </row>
-    <row r="110" spans="1:6" ht="18" customHeight="1">
+    <row r="110" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>114</v>
       </c>
@@ -3562,7 +3565,7 @@
       <c r="E110" s="1"/>
       <c r="F110" s="2"/>
     </row>
-    <row r="111" spans="1:6" ht="18" customHeight="1">
+    <row r="111" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>115</v>
       </c>
@@ -3578,7 +3581,7 @@
       <c r="E111" s="1"/>
       <c r="F111" s="2"/>
     </row>
-    <row r="112" spans="1:6" ht="18" customHeight="1">
+    <row r="112" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>116</v>
       </c>
@@ -3594,7 +3597,7 @@
       <c r="E112" s="1"/>
       <c r="F112" s="2"/>
     </row>
-    <row r="113" spans="1:6" ht="18" customHeight="1">
+    <row r="113" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>118</v>
       </c>
@@ -3610,7 +3613,7 @@
       <c r="E113" s="1"/>
       <c r="F113" s="2"/>
     </row>
-    <row r="114" spans="1:6" ht="18" customHeight="1">
+    <row r="114" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>120</v>
       </c>
@@ -3626,7 +3629,7 @@
       <c r="E114" s="1"/>
       <c r="F114" s="2"/>
     </row>
-    <row r="115" spans="1:6" ht="18" customHeight="1">
+    <row r="115" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>121</v>
       </c>
@@ -3642,7 +3645,7 @@
       <c r="E115" s="1"/>
       <c r="F115" s="2"/>
     </row>
-    <row r="116" spans="1:6" ht="18" customHeight="1">
+    <row r="116" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>122</v>
       </c>
@@ -3658,7 +3661,7 @@
       <c r="E116" s="1"/>
       <c r="F116" s="2"/>
     </row>
-    <row r="117" spans="1:6" ht="18" customHeight="1">
+    <row r="117" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>123</v>
       </c>
@@ -3674,7 +3677,7 @@
       <c r="E117" s="1"/>
       <c r="F117" s="2"/>
     </row>
-    <row r="118" spans="1:6" ht="18" customHeight="1">
+    <row r="118" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>124</v>
       </c>
@@ -3690,7 +3693,7 @@
       <c r="E118" s="1"/>
       <c r="F118" s="2"/>
     </row>
-    <row r="119" spans="1:6" ht="18" customHeight="1">
+    <row r="119" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>125</v>
       </c>
@@ -3706,7 +3709,7 @@
       <c r="E119" s="1"/>
       <c r="F119" s="2"/>
     </row>
-    <row r="120" spans="1:6" ht="18" customHeight="1">
+    <row r="120" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>126</v>
       </c>
@@ -3722,7 +3725,7 @@
       <c r="E120" s="1"/>
       <c r="F120" s="2"/>
     </row>
-    <row r="121" spans="1:6" ht="18" customHeight="1">
+    <row r="121" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>127</v>
       </c>
@@ -3738,7 +3741,7 @@
       <c r="E121" s="1"/>
       <c r="F121" s="2"/>
     </row>
-    <row r="122" spans="1:6" ht="18" customHeight="1">
+    <row r="122" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>128</v>
       </c>
@@ -3754,7 +3757,7 @@
       <c r="E122" s="1"/>
       <c r="F122" s="2"/>
     </row>
-    <row r="123" spans="1:6" ht="18" customHeight="1">
+    <row r="123" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>129</v>
       </c>
@@ -3770,7 +3773,7 @@
       <c r="E123" s="1"/>
       <c r="F123" s="2"/>
     </row>
-    <row r="124" spans="1:6" ht="18" customHeight="1">
+    <row r="124" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>130</v>
       </c>
@@ -3786,7 +3789,7 @@
       <c r="E124" s="1"/>
       <c r="F124" s="2"/>
     </row>
-    <row r="125" spans="1:6" ht="18" customHeight="1">
+    <row r="125" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>131</v>
       </c>
@@ -3802,7 +3805,7 @@
       <c r="E125" s="1"/>
       <c r="F125" s="2"/>
     </row>
-    <row r="126" spans="1:6" ht="18" customHeight="1">
+    <row r="126" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>133</v>
       </c>
@@ -3813,12 +3816,12 @@
         <v>1</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="2"/>
     </row>
-    <row r="127" spans="1:6" ht="18" customHeight="1">
+    <row r="127" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>134</v>
       </c>
@@ -3834,7 +3837,7 @@
       <c r="E127" s="1"/>
       <c r="F127" s="2"/>
     </row>
-    <row r="128" spans="1:6" ht="18" customHeight="1">
+    <row r="128" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>135</v>
       </c>
@@ -3850,7 +3853,7 @@
       <c r="E128" s="1"/>
       <c r="F128" s="2"/>
     </row>
-    <row r="129" spans="1:6" ht="18" customHeight="1">
+    <row r="129" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>136</v>
       </c>
@@ -3866,7 +3869,7 @@
       <c r="E129" s="1"/>
       <c r="F129" s="2"/>
     </row>
-    <row r="130" spans="1:6" ht="18" customHeight="1">
+    <row r="130" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>137</v>
       </c>
@@ -3882,7 +3885,7 @@
       <c r="E130" s="1"/>
       <c r="F130" s="2"/>
     </row>
-    <row r="131" spans="1:6" ht="18" customHeight="1">
+    <row r="131" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>139</v>
       </c>
@@ -3898,7 +3901,7 @@
       <c r="E131" s="1"/>
       <c r="F131" s="2"/>
     </row>
-    <row r="132" spans="1:6" ht="18" customHeight="1">
+    <row r="132" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>140</v>
       </c>
@@ -3914,7 +3917,7 @@
       <c r="E132" s="1"/>
       <c r="F132" s="2"/>
     </row>
-    <row r="133" spans="1:6" ht="18" customHeight="1">
+    <row r="133" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>142</v>
       </c>
@@ -3930,7 +3933,7 @@
       <c r="E133" s="1"/>
       <c r="F133" s="2"/>
     </row>
-    <row r="134" spans="1:6" ht="18" customHeight="1">
+    <row r="134" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>143</v>
       </c>
@@ -3946,7 +3949,7 @@
       <c r="E134" s="1"/>
       <c r="F134" s="2"/>
     </row>
-    <row r="135" spans="1:6" ht="18" customHeight="1">
+    <row r="135" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>145</v>
       </c>
@@ -3960,7 +3963,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="18" customHeight="1">
+    <row r="136" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>147</v>
       </c>
@@ -3974,7 +3977,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="18" customHeight="1">
+    <row r="137" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>149</v>
       </c>
@@ -3988,7 +3991,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="18" customHeight="1">
+    <row r="138" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>151</v>
       </c>
@@ -4002,7 +4005,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="18" customHeight="1">
+    <row r="139" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>152</v>
       </c>
@@ -4016,7 +4019,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="18" customHeight="1">
+    <row r="140" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>153</v>
       </c>
@@ -4030,7 +4033,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="18" customHeight="1">
+    <row r="141" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>155</v>
       </c>
@@ -4044,7 +4047,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="18" customHeight="1">
+    <row r="142" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>156</v>
       </c>
@@ -4058,7 +4061,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="18" customHeight="1">
+    <row r="143" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>157</v>
       </c>
@@ -4072,12 +4075,12 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="18" customHeight="1">
+    <row r="144" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>1</v>
@@ -4086,7 +4089,7 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="18" customHeight="1">
+    <row r="145" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>159</v>
       </c>
@@ -4100,7 +4103,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="18" customHeight="1">
+    <row r="146" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>160</v>
       </c>
@@ -4114,7 +4117,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="18" customHeight="1">
+    <row r="147" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>161</v>
       </c>
@@ -4128,7 +4131,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="18" customHeight="1">
+    <row r="148" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>163</v>
       </c>
@@ -4142,7 +4145,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="18" customHeight="1">
+    <row r="149" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>165</v>
       </c>
@@ -4162,7 +4165,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="18" customHeight="1">
+    <row r="150" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>167</v>
       </c>
@@ -4176,7 +4179,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="18" customHeight="1">
+    <row r="151" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>168</v>
       </c>
@@ -4190,7 +4193,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="18" customHeight="1">
+    <row r="152" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>170</v>
       </c>
@@ -4204,7 +4207,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="18" customHeight="1">
+    <row r="153" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>171</v>
       </c>
@@ -4218,7 +4221,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="18" customHeight="1">
+    <row r="154" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>172</v>
       </c>
@@ -4232,7 +4235,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="18" customHeight="1">
+    <row r="155" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>173</v>
       </c>
@@ -4246,7 +4249,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="18" customHeight="1">
+    <row r="156" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
         <v>175</v>
       </c>
@@ -4261,7 +4264,7 @@
       </c>
       <c r="F156" s="2"/>
     </row>
-    <row r="157" spans="1:6" ht="18" customHeight="1">
+    <row r="157" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>176</v>
       </c>
@@ -4276,12 +4279,12 @@
       </c>
       <c r="F157" s="2"/>
     </row>
-    <row r="158" spans="1:6" ht="18" customHeight="1">
+    <row r="158" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>1</v>
@@ -4291,12 +4294,12 @@
       </c>
       <c r="F158" s="2"/>
     </row>
-    <row r="159" spans="1:6" ht="18" customHeight="1">
+    <row r="159" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>1</v>
@@ -4306,12 +4309,12 @@
       </c>
       <c r="F159" s="2"/>
     </row>
-    <row r="160" spans="1:6" ht="18" customHeight="1">
+    <row r="160" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>1</v>
@@ -4321,12 +4324,12 @@
       </c>
       <c r="F160" s="2"/>
     </row>
-    <row r="161" spans="1:6" ht="18" customHeight="1">
+    <row r="161" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>1</v>
@@ -4336,7 +4339,7 @@
       </c>
       <c r="F161" s="2"/>
     </row>
-    <row r="162" spans="1:6" ht="18" customHeight="1">
+    <row r="162" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>177</v>
       </c>
@@ -4351,7 +4354,7 @@
       </c>
       <c r="F162" s="2"/>
     </row>
-    <row r="163" spans="1:6" ht="18" customHeight="1">
+    <row r="163" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>179</v>
       </c>
@@ -4366,7 +4369,7 @@
       </c>
       <c r="F163" s="2"/>
     </row>
-    <row r="164" spans="1:6" ht="18" customHeight="1">
+    <row r="164" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>181</v>
       </c>
@@ -4381,7 +4384,7 @@
       </c>
       <c r="F164" s="2"/>
     </row>
-    <row r="165" spans="1:6" ht="18" customHeight="1">
+    <row r="165" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>183</v>
       </c>
@@ -4396,7 +4399,7 @@
       </c>
       <c r="F165" s="2"/>
     </row>
-    <row r="166" spans="1:6" ht="18" customHeight="1">
+    <row r="166" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>185</v>
       </c>
@@ -4411,7 +4414,7 @@
       </c>
       <c r="F166" s="2"/>
     </row>
-    <row r="167" spans="1:6" ht="18" customHeight="1">
+    <row r="167" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>187</v>
       </c>
@@ -4426,9 +4429,9 @@
       </c>
       <c r="F167" s="2"/>
     </row>
-    <row r="168" spans="1:6" ht="18" customHeight="1">
+    <row r="168" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>189</v>
@@ -4441,7 +4444,7 @@
       </c>
       <c r="F168" s="2"/>
     </row>
-    <row r="169" spans="1:6" ht="18" customHeight="1">
+    <row r="169" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>190</v>
       </c>
@@ -4455,7 +4458,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="18" customHeight="1">
+    <row r="170" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>192</v>
       </c>
@@ -4470,12 +4473,12 @@
       </c>
       <c r="F170" s="2"/>
     </row>
-    <row r="171" spans="1:6" ht="18" customHeight="1">
+    <row r="171" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>1</v>
@@ -4490,7 +4493,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="18" customHeight="1">
+    <row r="172" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>195</v>
       </c>
@@ -4505,7 +4508,7 @@
       </c>
       <c r="F172" s="2"/>
     </row>
-    <row r="173" spans="1:6" ht="18" customHeight="1">
+    <row r="173" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>197</v>
       </c>
@@ -4520,12 +4523,12 @@
       </c>
       <c r="F173" s="2"/>
     </row>
-    <row r="174" spans="1:6" ht="18" customHeight="1">
+    <row r="174" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>199</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>1</v>
@@ -4535,7 +4538,7 @@
       </c>
       <c r="F174" s="2"/>
     </row>
-    <row r="175" spans="1:6" ht="18" customHeight="1">
+    <row r="175" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>200</v>
       </c>
@@ -4550,7 +4553,7 @@
       </c>
       <c r="F175" s="2"/>
     </row>
-    <row r="176" spans="1:6" ht="18" customHeight="1">
+    <row r="176" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>304</v>
       </c>
@@ -4565,7 +4568,7 @@
       </c>
       <c r="F176" s="2"/>
     </row>
-    <row r="177" spans="1:4" ht="18" customHeight="1">
+    <row r="177" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
         <v>313</v>
       </c>
@@ -4579,9 +4582,9 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="178" spans="1:4" ht="18" customHeight="1">
+    <row r="178" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>316</v>
@@ -4593,9 +4596,9 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="179" spans="1:4" ht="18" customHeight="1">
+    <row r="179" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>319</v>
@@ -4607,9 +4610,9 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="180" spans="1:4" ht="18" customHeight="1">
+    <row r="180" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>320</v>
@@ -4621,9 +4624,9 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="181" spans="1:4" ht="18" customHeight="1">
+    <row r="181" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>322</v>
@@ -4635,9 +4638,9 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="182" spans="1:4" ht="18" customHeight="1">
+    <row r="182" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>324</v>
@@ -4649,9 +4652,9 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="183" spans="1:4" ht="18" customHeight="1">
+    <row r="183" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>327</v>
@@ -4663,9 +4666,9 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="184" spans="1:4" ht="18" customHeight="1">
+    <row r="184" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>328</v>
@@ -4677,9 +4680,9 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="185" spans="1:4" ht="18" customHeight="1">
+    <row r="185" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>332</v>
@@ -4691,12 +4694,12 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="186" spans="1:4" ht="18" customHeight="1">
+    <row r="186" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>1</v>
@@ -4705,12 +4708,12 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="187" spans="1:4" ht="18" customHeight="1">
+    <row r="187" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>1</v>
@@ -4719,12 +4722,12 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="188" spans="1:4" ht="18" customHeight="1">
+    <row r="188" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>1</v>
@@ -4733,12 +4736,12 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="189" spans="1:4" ht="18" customHeight="1">
+    <row r="189" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>1</v>
@@ -4747,12 +4750,12 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="190" spans="1:4" ht="18" customHeight="1">
+    <row r="190" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>1</v>
